--- a/OUTPUT/direct_P74171_Synechocystis_sp__PCC_6803.xlsx
+++ b/OUTPUT/direct_P74171_Synechocystis_sp__PCC_6803.xlsx
@@ -486,7 +486,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.0608</v>
+        <v>0.06097560975609756</v>
       </c>
     </row>
     <row r="3">
@@ -515,7 +515,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.9442</v>
+        <v>0.9440223910435825</v>
       </c>
     </row>
     <row r="4">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.5798</v>
+        <v>0.5797680927628949</v>
       </c>
     </row>
   </sheetData>
